--- a/Paket_4_Bahasa_Indonesia_TKA_SD.xlsx
+++ b/Paket_4_Bahasa_Indonesia_TKA_SD.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Paket 4 Bahasa" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -471,27 +471,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[Paket 4] Soal Bahasa 1: contoh soal pemahaman teks.</t>
+          <t>Berdasarkan teks 'Komodo: Sang Naga Terakhir dari Nusa Tenggara', di pulau manakah satwa komodo dapat ditemukan di habitat aslinya?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Pulau Bali, Lombok, dan Sumbawa</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Pulau Komodo, Rinca, Gili Motang, dan sebagian Flores</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Pulau Kalimantan dan pedalaman Sumatera</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Pulau Sulawesi dan Kepulauan Maluku</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -502,7 +502,11 @@
       <c r="H2" t="n">
         <v>60</v>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -512,27 +516,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[Paket 4] Soal Bahasa 2: contoh soal pemahaman teks.</t>
+          <t>Bagaimana cara komodo melumpuhkan hewan mangsa buruannya?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Melilit tubuh mangsa hingga remuk seperti ular piton</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Menyemprotkan cairan asam dari dalam lambungnya</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Menggigit mangsa dengan gigi tajam dan menyuntikkan bisa yang mencegah pembekuan darah</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Menjatuhkan mangsa menggunakan hantaman ekornya yang panjang</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -543,7 +547,11 @@
       <c r="H3" t="n">
         <v>60</v>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -553,27 +561,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[Paket 4] Soal Bahasa 3: contoh soal pemahaman teks.</t>
+          <t>Makna istilah 'satwa endemik' pada teks informasi di atas adalah....</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Satwa yang hidup di perairan air tawar dan air laut</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Satwa yang hanya hidup secara alami di wilayah geografis tertentu dan tidak ditemukan di tempat lain</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Satwa liar yang telah berhasil dijinakkan oleh manusia</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Satwa pemakan tumbuhan dan biji-bijian di hutan tropis</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -584,37 +592,41 @@
       <c r="H4" t="n">
         <v>60</v>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Multiple</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[Paket 4] Soal Bahasa 4: contoh soal pemahaman teks.</t>
+          <t>Manakah pernyataan berikut yang BENAR mengenai ciri fisik dan kemampuan komodo sesuai teks bacaan?  [Pilihan Ganda Kompleks: Jawaban benar lebih dari satu]</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Komodo mendeteksi bau mangsanya menggunakan lidah yang bercabang kuning.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Panjang tubuh komodo dewasa dapat mencapai 3 meter.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Komodo tergolong hewan herbivor pemakan dedaunan pohon bakau.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Kawasan Taman Nasional Komodo ditetapkan sebagai cagar biosfer dunia yang dilindungi.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -625,7 +637,11 @@
       <c r="H5" t="n">
         <v>60</v>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -635,27 +651,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[Paket 4] Soal Bahasa 5: contoh soal pemahaman teks.</t>
+          <t>Ide pokok yang terdapat pada paragraf kedua teks informasi tersebut adalah....</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Sejarah penemuan kadal komodo oleh para penjelajah Eropa</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Ciri predator komodo, cara melumpuhkan mangsa, dan upaya perlindungannya</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Daftar hewan langka yang hidup di Kepulauan Nusa Tenggara</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Kandungan mineral air laut di kawasan Taman Nasional Komodo</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -666,17 +682,21 @@
       <c r="H6" t="n">
         <v>60</v>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[Paket 4] Soal Bahasa 6: contoh soal pemahaman teks.</t>
+          <t>Tentukan kebenaran dari pernyataan berikut berdasarkan teks informasi komodo!  [Pilihan Ganda Kompleks: Kategori Benar / Salah]</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -707,7 +727,11 @@
       <c r="H7" t="n">
         <v>60</v>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -717,27 +741,31 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[Paket 4] Soal Bahasa 7: contoh soal pemahaman teks.</t>
+          <t>Simpulan yang paling tepat dari teks bacaan komodo adalah.... Bacalah cerita fiksi berikut dengan cermat untuk menjawab soal nomor 8 sampai 14!
+Lompatan Cici si Tupai Pohon
+Di dahan pohon kenari yang menjulang tinggi, Cici si tupai kecil sedang bersedih. Cici sangat ingin melompati celah dahan selebar tiga meter menuju pohon jambu yang sedang berbuah lebat di seberang sungai kecil. Kemarin, saat mencoba melompat, Cici terpeleset dan jatuh ke tumpukan jerami di bawah pohon. Sejak kejadian itu, Cici gemetar dan takut untuk memanjat dahan yang tinggi.
+Kakek Tupai yang bijak menghampiri Cici dan memberinya sebuah biji kenari. "Cici, jatuh bukan berarti kau tidak bisa melompat. Seekor tupai yang hebat bukanlah tupai yang tidak pernah terpeleset, melainkan tupai yang berani bangkit dan belajar dari letak kesalahannya kemarin." Kakek Tupai kemudian menunjukkan cara menekuk kaki belakang lebih kuat sebagai pegas sebelum meluncur.
+Cici merenungi perkataan kakeknya. Ia kembali berlatih melompat dari dahan yang rendah terlebih dahulu. Hari demi hari ia melatih kekuatan kakinya tanpa mengeluh. Pada hari kelima, dengan penuh percaya diri, Cici meluncur dari dahan pohon kenari. Hap! Cici berhasil mendarat dengan anggun tepat di dahan pohon jambu. Cici tersenyum bangga karena telah berhasil menaklukkan rasa takut di dalam hatinya.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Komodo adalah satwa endemik purba Indonesia berukuran raksasa yang memiliki adaptasi predator unik dan wajib dilestarikan.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Komodo merupakan hewan purba yang harus dipindahkan ke seluruh kebun binatang dunia.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Populasi rusa di Nusa Tenggara habis karena dimangsa komodo setiap hari.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Bisa komodo dapat dimanfaatkan sebagai penawar racun bagi gigitan ular berbisa.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -748,7 +776,11 @@
       <c r="H8" t="n">
         <v>60</v>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -758,27 +790,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>[Paket 4] Soal Bahasa 8: contoh soal pemahaman teks.</t>
+          <t>Apa penyebab tokoh Cici merasa takut dan tidak berani memanjat dahan pohon yang tinggi?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Cici dimarahi oleh kakeknya karena merusak dahan pohon</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Cici trauma karena sebelumnya pernah terpeleset dan jatuh saat mencoba melompat</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Ada burung elang pemangsa yang mengintai di dahan pohon jambu</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Pohon jambu di seberang sungai telah ditebang oleh pemilik kebun</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -789,7 +821,11 @@
       <c r="H9" t="n">
         <v>60</v>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -799,27 +835,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>[Paket 4] Soal Bahasa 9: contoh soal pemahaman teks.</t>
+          <t>Bagaimana sifat Kakek Tupai dalam mendampingi Cici yang sedang trauma?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Suka mengejek dan membanding-bandingkan dengan tupai lain</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Bijaksana, sabar membimbing, dan memberi semangat hidup</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Mudah marah jika cucunya tidak berhasil melompat</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Acuh tak acuh dan membiarkan Cici menangis sendirian</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -830,7 +866,11 @@
       <c r="H10" t="n">
         <v>60</v>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -840,27 +880,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>[Paket 4] Soal Bahasa 10: contoh soal pemahaman teks.</t>
+          <t>Sikap positif apa yang ditunjukkan oleh Cici setelah merenungkan perkataan kakeknya?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Berhenti menjadi tupai pemanjat pohon</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Gigih berlatih kembali dari dahan rendah hingga menguasai teknik melompat</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Menunggu bantuan hewan lain untuk mengantarnya ke seberang</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Menangis menyesali nasibnya yang bertubuh kecil</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -871,37 +911,41 @@
       <c r="H11" t="n">
         <v>60</v>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>[Paket 4] Soal Bahasa 11: contoh soal pemahaman teks.</t>
+          <t>Manakah pernyataan nasihat Kakek Tupai yang memotivasi Cici untuk bangkit kembali?  [Pilihan Ganda Kompleks: Jawaban benar lebih dari satu]</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Jatuh bukan berarti kamu tidak bisa melompat.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Tupai yang hebat adalah tupai yang berani bangkit dan belajar dari kesalahannya.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Jangan pernah mencoba hal baru jika berisiko terpeleset.</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Menyerahlah sebelum kakimu terluka lebih parah.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -912,7 +956,11 @@
       <c r="H12" t="n">
         <v>60</v>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -922,27 +970,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[Paket 4] Soal Bahasa 12: contoh soal pemahaman teks.</t>
+          <t>Amanat moral yang dapat dipetik dari kisah perjuangan Cici si tupai adalah....</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Kegagalan adalah akhir dari segalanya sehingga kita tidak boleh mencoba lagi.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Jangan takut gagal, belajarlah dari kesalahan dan terus berlatih untuk mengalahkan rasa takut.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Pohon jambu lebih lezat buahnya daripada pohon kenari.</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Lompatlah setinggi mungkin tanpa perlu memperhatikan keselamatan diri.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -953,17 +1001,21 @@
       <c r="H13" t="n">
         <v>60</v>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Multiple</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>[Paket 4] Soal Bahasa 13: contoh soal pemahaman teks.</t>
+          <t>Tentukan kesesuaian dari pernyataan berikut terkait pesan moral fabel Cici si tupai!  [Pilihan Ganda Kompleks: Kategori Benar / Salah]</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -994,7 +1046,11 @@
       <c r="H14" t="n">
         <v>60</v>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1004,27 +1060,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>[Paket 4] Soal Bahasa 14: contoh soal pemahaman teks.</t>
+          <t>Ungkapan yang tepat untuk menggambarkan tekad pantang menyerah Cici dalam berlatih adalah....</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Keras kepala</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Patah arang</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Gigih berjuang</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Tebal muka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1035,7 +1091,11 @@
       <c r="H15" t="n">
         <v>60</v>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1045,27 +1105,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>[Paket 4] Soal Bahasa 15: contoh soal pemahaman teks.</t>
+          <t>Penulisan kata ulang yang tepat sesuai kaidah EBI terdapat pada kalimat....</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Kupu-kupu beterbangan di antara bunga bunga taman yang sedang mekar.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Kupu kupu beterbangan di antara bunga-bunga taman yang sedang mekar.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Kupu-kupu beterbangan di antara bunga-bunga taman yang sedang mekar.</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Kupu-kupu beterbangan di antara bunga_bunga taman yang sedang mekar.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1076,7 +1136,11 @@
       <c r="H16" t="n">
         <v>60</v>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1086,27 +1150,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>[Paket 4] Soal Bahasa 16: contoh soal pemahaman teks.</t>
+          <t>Penulisan kata baku yang benar terdapat pada kalimat....</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Siswa kelas 6 sedang melakukan praktek sains di laboratorium.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Siswa kelas 6 sedang melakukan praktik sains di laboratorium.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Siswa kelas 6 sedang melakukan praktek sains di laboratorim.</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Siswa kelas 6 sedang melakukan praktik sains di laborat.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1117,7 +1181,11 @@
       <c r="H17" t="n">
         <v>60</v>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1127,27 +1195,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>[Paket 4] Soal Bahasa 17: contoh soal pemahaman teks.</t>
+          <t>Kalimat berikut yang tepat dalam penulisan nama geografi sesuai EBI adalah....</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Kami menyeberangi selat Sunda menuju ke pelabuhan Bakauheni di pulau Sumatera.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Kami menyeberangi Selat Sunda menuju ke Pelabuhan Bakauheni di Pulau Sumatera.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Kami menyeberangi Selat sunda menuju ke pelabuhan bakauheni di pulau sumatera.</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Kami menyeberangi selat sunda menuju ke Pelabuhan Bakauheni di Pulau Sumatera.</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1158,37 +1226,46 @@
       <c r="H18" t="n">
         <v>60</v>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Multiple</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[Paket 4] Soal Bahasa 18: contoh soal pemahaman teks.</t>
+          <t>Perhatikan kalimat-kalimat berikut:
+(1) Dika belajar giat agar ia lulus ujian dengan nilai memuaskan.
+(2) Ibu menyiram bunga dan ayah membaca koran di teras.
+(3) Kami tidak jadi berolahraga di lapangan karena hujan turun sangat lebat.
+(4) Adik makan roti atau minum susu hangat.
+Manakah kalimat di atas yang termasuk KALIMAT MAJEMUK BERTINGKAT?  [Pilihan Ganda Kompleks: Jawaban benar lebih dari satu]</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  Kalimat (1)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  Kalimat (2)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  Kalimat (3)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  Kalimat (4)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1199,7 +1276,11 @@
       <c r="H19" t="n">
         <v>60</v>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1209,27 +1290,32 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>[Paket 4] Soal Bahasa 19: contoh soal pemahaman teks.</t>
+          <t>Perhatikan kalimat-kalimat acak berikut mengenai keindahan Candi Borobudur:
+(1) Dinding-dinding candi dihiasi ribuan relief batu yang menceritakan ajaran kebajikan.
+(2) Candi Borobudur merupakan candi Buddha terbesar di dunia yang terletak di Magelang.
+(3) Di puncak candi terdapat stupa utama berukuran besar yang dikelilingi puluhan stupa berlubang.
+(4) Kemegahan arsitektur masa lampau ini menarik kekaguman jutaan wisatawan mancanegara.
+Urutan kalimat yang padu untuk menyusun teks deskripsi adalah....</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A.  (2) - (1) - (3) - (4)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B.  (2) - (4) - (1) - (3)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C.  (1) - (3) - (2) - (4)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D.  (4) - (2) - (1) - (3)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1240,17 +1326,21 @@
       <c r="H20" t="n">
         <v>60</v>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Multiple</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>[Paket 4] Soal Bahasa 20: contoh soal pemahaman teks.</t>
+          <t>Tentukan kebenaran penggunaan huruf miring (cetak miring) dalam kalimat-kalimat berikut!  [Pilihan Ganda Kompleks: Kategori Benar / Salah]</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1281,7 +1371,11 @@
       <c r="H21" t="n">
         <v>60</v>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
